--- a/data/dividends_info_20260329.xlsx
+++ b/data/dividends_info_20260329.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,11 +491,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -504,45 +504,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2027-02-22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2027-02-24</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>IT0004998065</t>
+          <t>IT0001031084</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>6.659999847412109</v>
+        <v>50.75</v>
       </c>
       <c r="I2" t="n">
-        <v>7.507507679512727</v>
+        <v>1.379310344827586</v>
       </c>
       <c r="J2" t="n">
-        <v>22</v>
+        <v>330</v>
       </c>
       <c r="K2" t="n">
-        <v>24</v>
+        <v>332</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.65</v>
+        <v>0.06</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -551,45 +551,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>IT0004776628</t>
+          <t>IT0005337818</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>16.89999961853027</v>
+        <v>8.960000038146973</v>
       </c>
       <c r="I3" t="n">
-        <v>3.846153932969899</v>
+        <v>0.6696428542918696</v>
       </c>
       <c r="J3" t="n">
-        <v>22</v>
+        <v>260</v>
       </c>
       <c r="K3" t="n">
-        <v>24</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.54</v>
+        <v>0.077</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -598,45 +598,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>IT0005218380</t>
+          <t>IT0001469383</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>11.67500019073486</v>
+        <v>1.968000054359436</v>
       </c>
       <c r="I4" t="n">
-        <v>4.625267590389741</v>
+        <v>3.912601517943693</v>
       </c>
       <c r="J4" t="n">
-        <v>22</v>
+        <v>239</v>
       </c>
       <c r="K4" t="n">
-        <v>24</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -645,45 +645,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>NL0015435975</t>
+          <t>IT0005312027</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6.131999969482422</v>
+        <v>5.449999809265137</v>
       </c>
       <c r="I5" t="n">
-        <v>1.630789310138249</v>
+        <v>3.669724899072381</v>
       </c>
       <c r="J5" t="n">
-        <v>22</v>
+        <v>232</v>
       </c>
       <c r="K5" t="n">
-        <v>24</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -692,12 +692,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -707,30 +707,30 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>IT0005215329</t>
+          <t>IT0003128367</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>8.220000267028809</v>
+        <v>9.145999908447266</v>
       </c>
       <c r="I6" t="n">
-        <v>1.946471956233079</v>
+        <v>2.842772825307635</v>
       </c>
       <c r="J6" t="n">
-        <v>22</v>
+        <v>113</v>
       </c>
       <c r="K6" t="n">
-        <v>24</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.14</v>
+        <v>0.376</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -739,12 +739,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -754,30 +754,30 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>IT0001214433</t>
+          <t>IT0000214293</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>23.39999961853027</v>
+        <v>17.89999961853027</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5982906080440067</v>
+        <v>2.100558703983215</v>
       </c>
       <c r="J7" t="n">
-        <v>15</v>
+        <v>113</v>
       </c>
       <c r="K7" t="n">
-        <v>17</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -801,30 +801,30 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>IT0005418204</t>
+          <t>IT0004053440</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.470000028610229</v>
+        <v>4.945000171661377</v>
       </c>
       <c r="I8" t="n">
-        <v>4.081632573621466</v>
+        <v>2.426693545688664</v>
       </c>
       <c r="J8" t="n">
-        <v>15</v>
+        <v>106</v>
       </c>
       <c r="K8" t="n">
-        <v>17</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.034</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -833,12 +833,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -848,30 +848,30 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>IT0005379604</t>
+          <t>IT0001382024</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1.934999942779541</v>
+        <v>2.119999885559082</v>
       </c>
       <c r="I9" t="n">
-        <v>1.757105995112358</v>
+        <v>4.009434178699683</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.26</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -880,82 +880,4688 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>IT0003132476</t>
+          <t>IT0005561441</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>23.92499923706055</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>1.086729397245924</v>
+        <v>1.75</v>
       </c>
       <c r="J10" t="n">
-        <v>-6</v>
+        <v>99</v>
       </c>
       <c r="K10" t="n">
-        <v>-4</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>IT0004195308</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>30.29999923706055</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.4950495174156042</v>
+      </c>
+      <c r="J11" t="n">
+        <v>99</v>
+      </c>
+      <c r="K11" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ACEA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Straordinario</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>IT0001207098</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>21.8799991607666</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.142596021887785</v>
+      </c>
+      <c r="J12" t="n">
+        <v>85</v>
+      </c>
+      <c r="K12" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CAREL INDUSTRIES S.p.A.</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>IT0005331019</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9069767441860466</v>
+      </c>
+      <c r="J13" t="n">
+        <v>85</v>
+      </c>
+      <c r="K13" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ENAV S.p.A.</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>IT0005176406</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>5.125</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5.658536585365853</v>
+      </c>
+      <c r="J14" t="n">
+        <v>85</v>
+      </c>
+      <c r="K14" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HERA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>IT0001250932</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>3.901999950408936</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.100461354009801</v>
+      </c>
+      <c r="J15" t="n">
+        <v>85</v>
+      </c>
+      <c r="K15" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>IREN S.p.A.</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.1386</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>IT0003027817</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>2.414000034332275</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5.741507789097338</v>
+      </c>
+      <c r="J16" t="n">
+        <v>85</v>
+      </c>
+      <c r="K16" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Leonardo S.p.A.</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>IT0003856405</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>56.61999893188477</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.112681052427969</v>
+      </c>
+      <c r="J17" t="n">
+        <v>85</v>
+      </c>
+      <c r="K17" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>POWERSOFT S.p.A.</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>IT0005353815</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>17</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.588235294117647</v>
+      </c>
+      <c r="J18" t="n">
+        <v>85</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Poste Italiane S.p.A.</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>IT0003796171</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>19.79500007629395</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.294013623258032</v>
+      </c>
+      <c r="J19" t="n">
+        <v>85</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Snam S.p.A.</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.1813</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>IT0003153415</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>6.381999969482422</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.840802269930179</v>
+      </c>
+      <c r="J20" t="n">
+        <v>85</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>IT0003153621</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>7.570000171661377</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.434610225945849</v>
+      </c>
+      <c r="J21" t="n">
+        <v>85</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TERNA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>IT0003242622</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>9.562000274658203</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.896883413966452</v>
+      </c>
+      <c r="J22" t="n">
+        <v>85</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NL0015000K93</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4.396039603960396</v>
+      </c>
+      <c r="J23" t="n">
+        <v>67</v>
+      </c>
+      <c r="K23" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMAK S.p.A.</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>IT0001237053</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>0.8220000267028809</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.649634917937024</v>
+      </c>
+      <c r="J24" t="n">
+        <v>64</v>
+      </c>
+      <c r="K24" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FNM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>IT0000060886</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>0.460999995470047</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4.98915406204042</v>
+      </c>
+      <c r="J25" t="n">
+        <v>64</v>
+      </c>
+      <c r="K25" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>IT0004329733</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>2.525000095367432</v>
+      </c>
+      <c r="I26" t="n">
+        <v>7.128712602040787</v>
+      </c>
+      <c r="J26" t="n">
+        <v>57</v>
+      </c>
+      <c r="K26" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>EL.EN. S.p.A.</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>IT0005453250</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>12.1899995803833</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.050861432368802</v>
+      </c>
+      <c r="J27" t="n">
+        <v>57</v>
+      </c>
+      <c r="K27" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Neodecortech S.p.A.</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>IT0005275778</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>3.579999923706055</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4.189944223370775</v>
+      </c>
+      <c r="J28" t="n">
+        <v>57</v>
+      </c>
+      <c r="K28" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SABAF S.p.A.</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>IT0001042610</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>13.35000038146973</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4.344569164245573</v>
+      </c>
+      <c r="J29" t="n">
+        <v>57</v>
+      </c>
+      <c r="K29" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A2A S.p.A.</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>IT0001233417</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>2.374000072479248</v>
+      </c>
+      <c r="I30" t="n">
+        <v>4.380791778636691</v>
+      </c>
+      <c r="J30" t="n">
+        <v>50</v>
+      </c>
+      <c r="K30" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AMPLIFON S.p.A.</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>IT0004056880</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>9.11400032043457</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3.181917816590249</v>
+      </c>
+      <c r="J31" t="n">
+        <v>50</v>
+      </c>
+      <c r="K31" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Interim</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>IT0001469383</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>1.968000054359436</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3.912601517943693</v>
+      </c>
+      <c r="J32" t="n">
+        <v>50</v>
+      </c>
+      <c r="K32" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>IT0000062072</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>33.52000045776367</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4.892601365165419</v>
+      </c>
+      <c r="J33" t="n">
+        <v>50</v>
+      </c>
+      <c r="K33" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AZIMUT HOLDING S.p.A.</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>IT0003261697</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>32.33000183105469</v>
+      </c>
+      <c r="I34" t="n">
+        <v>6.186204413013344</v>
+      </c>
+      <c r="J34" t="n">
+        <v>50</v>
+      </c>
+      <c r="K34" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Ariston Holding N.V.</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>NL0015000N33</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>3.575999975204468</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2.796420601045508</v>
+      </c>
+      <c r="J35" t="n">
+        <v>50</v>
+      </c>
+      <c r="K35" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Avio S.p.A.</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.14846</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>IT0005119810</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.4603410852713178</v>
+      </c>
+      <c r="J36" t="n">
+        <v>50</v>
+      </c>
+      <c r="K36" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BANCA IFIS S.p.A.</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>IT0003188064</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>21.84000015258789</v>
+      </c>
+      <c r="I37" t="n">
+        <v>4.212454183023375</v>
+      </c>
+      <c r="J37" t="n">
+        <v>50</v>
+      </c>
+      <c r="K37" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BREMBO N.V.</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>NL0015001KT6</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>8.064999580383301</v>
+      </c>
+      <c r="I38" t="n">
+        <v>3.719777006928772</v>
+      </c>
+      <c r="J38" t="n">
+        <v>50</v>
+      </c>
+      <c r="K38" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>IT0004764699</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>71.77999877929688</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.448871576604097</v>
+      </c>
+      <c r="J39" t="n">
+        <v>50</v>
+      </c>
+      <c r="K39" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Banca Generali S.p.A.</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Interim</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>IT0001031084</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>50.75</v>
+      </c>
+      <c r="I40" t="n">
+        <v>4.334975369458129</v>
+      </c>
+      <c r="J40" t="n">
+        <v>50</v>
+      </c>
+      <c r="K40" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>IT0005508921</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>7.497000217437744</v>
+      </c>
+      <c r="I41" t="n">
+        <v>11.47125483602991</v>
+      </c>
+      <c r="J41" t="n">
+        <v>50</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Bper Banca S.P.A.</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>IT0000066123</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>10.86499977111816</v>
+      </c>
+      <c r="I42" t="n">
+        <v>5.154164857772179</v>
+      </c>
+      <c r="J42" t="n">
+        <v>50</v>
+      </c>
+      <c r="K42" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>IT0001472171</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2.285714285714286</v>
+      </c>
+      <c r="J43" t="n">
+        <v>50</v>
+      </c>
+      <c r="K43" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CALTAGIRONE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>IT0003127930</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>8.539999961853027</v>
+      </c>
+      <c r="I44" t="n">
+        <v>3.512880577752431</v>
+      </c>
+      <c r="J44" t="n">
+        <v>50</v>
+      </c>
+      <c r="K44" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CELLULARLINE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>IT0005244618</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>2.240000009536743</v>
+      </c>
+      <c r="I45" t="n">
+        <v>4.821428550901461</v>
+      </c>
+      <c r="J45" t="n">
+        <v>50</v>
+      </c>
+      <c r="K45" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CEMBRE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>IT0001128047</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>64.80000305175781</v>
+      </c>
+      <c r="I46" t="n">
+        <v>3.179012195963344</v>
+      </c>
+      <c r="J46" t="n">
+        <v>50</v>
+      </c>
+      <c r="K46" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CREDITO EMILIANO S.p.A.</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>IT0003121677</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>14.26000022888184</v>
+      </c>
+      <c r="I47" t="n">
+        <v>5.259466956255508</v>
+      </c>
+      <c r="J47" t="n">
+        <v>50</v>
+      </c>
+      <c r="K47" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Cementir Holding N.V.</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>NL0013995087</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>15.10000038146973</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1.986754916696235</v>
+      </c>
+      <c r="J48" t="n">
+        <v>50</v>
+      </c>
+      <c r="K48" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Comer Industries S.p.A.</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>IT0005246191</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>40.40000152587891</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2.103960316574538</v>
+      </c>
+      <c r="J49" t="n">
+        <v>50</v>
+      </c>
+      <c r="K49" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>DE' LONGHI S.p.A.</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>IT0003115950</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>29.07999992370605</v>
+      </c>
+      <c r="I50" t="n">
+        <v>2.922971121836486</v>
+      </c>
+      <c r="J50" t="n">
+        <v>50</v>
+      </c>
+      <c r="K50" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>DiaSorin S.p.A</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>IT0003492391</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>58.2599983215332</v>
+      </c>
+      <c r="I51" t="n">
+        <v>2.23137665199608</v>
+      </c>
+      <c r="J51" t="n">
+        <v>50</v>
+      </c>
+      <c r="K51" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Directa SIM S.P.A.</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>IT0001463063</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>6.659999847412109</v>
+      </c>
+      <c r="I52" t="n">
+        <v>9.009009215415272</v>
+      </c>
+      <c r="J52" t="n">
+        <v>50</v>
+      </c>
+      <c r="K52" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>EQUITA GROUP S.p.A.</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Interim</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>IT0005312027</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>5.449999809265137</v>
+      </c>
+      <c r="I53" t="n">
+        <v>3.669724899072381</v>
+      </c>
+      <c r="J53" t="n">
+        <v>50</v>
+      </c>
+      <c r="K53" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ERG S.p.A.</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>IT0001157020</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>21.31999969482422</v>
+      </c>
+      <c r="I54" t="n">
+        <v>4.690431586838936</v>
+      </c>
+      <c r="J54" t="n">
+        <v>50</v>
+      </c>
+      <c r="K54" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Enervit S.p.A.</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>IT0004356751</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>4.139999866485596</v>
+      </c>
+      <c r="I55" t="n">
+        <v>5.193236882456988</v>
+      </c>
+      <c r="J55" t="n">
+        <v>50</v>
+      </c>
+      <c r="K55" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>F.I.L.A. S.p.A.</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>IT0004967292</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>9.329999923706055</v>
+      </c>
+      <c r="I56" t="n">
+        <v>2.572347287915811</v>
+      </c>
+      <c r="J56" t="n">
+        <v>50</v>
+      </c>
+      <c r="K56" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>FinecoBank S.p.A.</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>IT0000072170</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>18.63999938964844</v>
+      </c>
+      <c r="I57" t="n">
+        <v>4.238197563669019</v>
+      </c>
+      <c r="J57" t="n">
+        <v>50</v>
+      </c>
+      <c r="K57" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>IT0005345233</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>4.485000133514404</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2.073578533589163</v>
+      </c>
+      <c r="J58" t="n">
+        <v>50</v>
+      </c>
+      <c r="K58" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>INTERPUMP GROUP S.p.A.</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>IT0001078911</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>32.61999893188477</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1.072961408523802</v>
+      </c>
+      <c r="J59" t="n">
+        <v>50</v>
+      </c>
+      <c r="K59" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>IRCE s.p.a</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>IT0001077780</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>1.960000038146973</v>
+      </c>
+      <c r="I60" t="n">
+        <v>3.061224430216099</v>
+      </c>
+      <c r="J60" t="n">
+        <v>50</v>
+      </c>
+      <c r="K60" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>IT0003411417</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>11.89999961853027</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1.680672322783665</v>
+      </c>
+      <c r="J61" t="n">
+        <v>50</v>
+      </c>
+      <c r="K61" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Industrie De Nora S.p.A.</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>IT0005186371</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>5.550000190734863</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1.855855792076324</v>
+      </c>
+      <c r="J62" t="n">
+        <v>50</v>
+      </c>
+      <c r="K62" t="n">
+        <v>-313</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Intesa Sanpaolo S.p.A.</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>IT0000072618</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>5.098000049591064</v>
+      </c>
+      <c r="I63" t="n">
+        <v>3.72695170952854</v>
+      </c>
+      <c r="J63" t="n">
+        <v>50</v>
+      </c>
+      <c r="K63" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Italgas S.p.A.</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>IT0005211237</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>9.779999732971191</v>
+      </c>
+      <c r="I64" t="n">
+        <v>4.417178034715112</v>
+      </c>
+      <c r="J64" t="n">
+        <v>50</v>
+      </c>
+      <c r="K64" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Lottomatica Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>IT0005541336</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>24.97999954223633</v>
+      </c>
+      <c r="I65" t="n">
+        <v>1.761409159580029</v>
+      </c>
+      <c r="J65" t="n">
+        <v>50</v>
+      </c>
+      <c r="K65" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>MARR S.p.A.</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>IT0003428445</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>7.289999961853027</v>
+      </c>
+      <c r="I66" t="n">
+        <v>6.447187962406131</v>
+      </c>
+      <c r="J66" t="n">
+        <v>50</v>
+      </c>
+      <c r="K66" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Moncler S.p.A.</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>IT0004965148</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>50.13999938964844</v>
+      </c>
+      <c r="I67" t="n">
+        <v>2.792181924695105</v>
+      </c>
+      <c r="J67" t="n">
+        <v>50</v>
+      </c>
+      <c r="K67" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Nexi S.p.A.</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>IT0005366767</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>2.994999885559082</v>
+      </c>
+      <c r="I68" t="n">
+        <v>10.01669487356252</v>
+      </c>
+      <c r="J68" t="n">
+        <v>50</v>
+      </c>
+      <c r="K68" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Next Geosolutions Europe S.p.A.</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>IT0005594418</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>11.80000019073486</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1.016949136104436</v>
+      </c>
+      <c r="J69" t="n">
+        <v>50</v>
+      </c>
+      <c r="K69" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>OMER S.p.A.</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>IT0005453748</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>3.480000019073486</v>
+      </c>
+      <c r="I70" t="n">
+        <v>4.885057444489921</v>
+      </c>
+      <c r="J70" t="n">
+        <v>50</v>
+      </c>
+      <c r="K70" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Pattern S.p.A.</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>IT0005378143</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>3.029999971389771</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1.155115522458126</v>
+      </c>
+      <c r="J71" t="n">
+        <v>50</v>
+      </c>
+      <c r="K71" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>RAI WAY S.p.A.</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>IT0005054967</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>5.78000020980835</v>
+      </c>
+      <c r="I72" t="n">
+        <v>5.709342353310087</v>
+      </c>
+      <c r="J72" t="n">
+        <v>50</v>
+      </c>
+      <c r="K72" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>RCS MediaGroup S.p.A.</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>IT0004931496</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>0.925000011920929</v>
+      </c>
+      <c r="I73" t="n">
+        <v>7.567567470040612</v>
+      </c>
+      <c r="J73" t="n">
+        <v>50</v>
+      </c>
+      <c r="K73" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>RECORDATI S.p.A.</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>IT0003828271</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>48.88000106811523</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1.452536793136729</v>
+      </c>
+      <c r="J74" t="n">
+        <v>50</v>
+      </c>
+      <c r="K74" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>REPLY S.p.A.</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>IT0005282865</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>78.09999847412109</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1.728553170775452</v>
+      </c>
+      <c r="J75" t="n">
+        <v>50</v>
+      </c>
+      <c r="K75" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>SAIPEM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>IT0005495657</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>3.714999914169312</v>
+      </c>
+      <c r="I76" t="n">
+        <v>4.57604317436472</v>
+      </c>
+      <c r="J76" t="n">
+        <v>50</v>
+      </c>
+      <c r="K76" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>SOL S.p.A.</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>IT0001206769</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>56.20000076293945</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.800711732902232</v>
+      </c>
+      <c r="J77" t="n">
+        <v>50</v>
+      </c>
+      <c r="K77" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>SYS-DAT S.p.A.</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>IT0005595423</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>5</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J78" t="n">
+        <v>50</v>
+      </c>
+      <c r="K78" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Sanlorenzo S.p.A.</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>IT0003549422</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>29.70000076293945</v>
+      </c>
+      <c r="I79" t="n">
+        <v>3.53535344453668</v>
+      </c>
+      <c r="J79" t="n">
+        <v>50</v>
+      </c>
+      <c r="K79" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>TECHNOGYM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>IT0005162406</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>17.02000045776367</v>
+      </c>
+      <c r="I80" t="n">
+        <v>2.232667390009752</v>
+      </c>
+      <c r="J80" t="n">
+        <v>50</v>
+      </c>
+      <c r="K80" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>TENARIS S.A.</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
           <t>DOLLARI USA</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>LU2598331598</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>25.40999984741211</v>
+      </c>
+      <c r="I81" t="n">
+        <v>2.361275102727351</v>
+      </c>
+      <c r="J81" t="n">
+        <v>50</v>
+      </c>
+      <c r="K81" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>IT0001454435</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>28</v>
+      </c>
+      <c r="I82" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J82" t="n">
+        <v>50</v>
+      </c>
+      <c r="K82" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>WEBUILD S.p.A.</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>IT0003865570</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>2.267999887466431</v>
+      </c>
+      <c r="I83" t="n">
+        <v>11.46384536599093</v>
+      </c>
+      <c r="J83" t="n">
+        <v>50</v>
+      </c>
+      <c r="K83" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>IT0001006128</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>9.199999809265137</v>
+      </c>
+      <c r="I84" t="n">
+        <v>3.804347904958889</v>
+      </c>
+      <c r="J84" t="n">
+        <v>43</v>
+      </c>
+      <c r="K84" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Ecomembrane S.p.A.</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>IT0005543332</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>4.599999904632568</v>
+      </c>
+      <c r="I85" t="n">
+        <v>2.086956565006019</v>
+      </c>
+      <c r="J85" t="n">
+        <v>43</v>
+      </c>
+      <c r="K85" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Intred S.p.A.</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
         <is>
           <t>Interim</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>NL0000226223</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>28.5049991607666</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.3157340910357689</v>
-      </c>
-      <c r="J11" t="n">
-        <v>-6</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-4</v>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>IT0005337818</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>8.960000038146973</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.6696428542918696</v>
+      </c>
+      <c r="J86" t="n">
+        <v>43</v>
+      </c>
+      <c r="K86" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Orsero S.p.A.</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>IT0005138703</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>14.60000038146973</v>
+      </c>
+      <c r="I87" t="n">
+        <v>3.424657444766908</v>
+      </c>
+      <c r="J87" t="n">
+        <v>43</v>
+      </c>
+      <c r="K87" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Porto Aviation Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>IT0005545238</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>10.10000038146973</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.8415841266298152</v>
+      </c>
+      <c r="J88" t="n">
+        <v>43</v>
+      </c>
+      <c r="K88" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Racing Force S.p.A.</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>IT0005466963</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>4.650000095367432</v>
+      </c>
+      <c r="I89" t="n">
+        <v>2.04301071078781</v>
+      </c>
+      <c r="J89" t="n">
+        <v>43</v>
+      </c>
+      <c r="K89" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ZIGNAGO VETRO S.p.A.</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>IT0004171440</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>7</v>
+      </c>
+      <c r="I90" t="n">
+        <v>3.142857142857143</v>
+      </c>
+      <c r="J90" t="n">
+        <v>43</v>
+      </c>
+      <c r="K90" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>IGD SIIQ S.p.A.</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>IT0005322612</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>3.815000057220459</v>
+      </c>
+      <c r="I91" t="n">
+        <v>3.931847909572177</v>
+      </c>
+      <c r="J91" t="n">
+        <v>36</v>
+      </c>
+      <c r="K91" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>INTERCOS S.p.A.</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0.197169</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>IT0005455875</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>12.27999973297119</v>
+      </c>
+      <c r="I92" t="n">
+        <v>1.605610784099702</v>
+      </c>
+      <c r="J92" t="n">
+        <v>36</v>
+      </c>
+      <c r="K92" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ITALMOBILIARE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>IT0005253205</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="I93" t="n">
+        <v>4.150943396226416</v>
+      </c>
+      <c r="J93" t="n">
+        <v>36</v>
+      </c>
+      <c r="K93" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>LU-VE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>IT0005107492</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>37.40000152587891</v>
+      </c>
+      <c r="I94" t="n">
+        <v>1.256684440707265</v>
+      </c>
+      <c r="J94" t="n">
+        <v>36</v>
+      </c>
+      <c r="K94" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>PLC S.p.A.</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>IT0005339160</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>2.430000066757202</v>
+      </c>
+      <c r="I95" t="n">
+        <v>4.52674884683412</v>
+      </c>
+      <c r="J95" t="n">
+        <v>36</v>
+      </c>
+      <c r="K95" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Pharmanutra S.p.A.</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>IT0005274094</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>74.69999694824219</v>
+      </c>
+      <c r="I96" t="n">
+        <v>1.606425768439389</v>
+      </c>
+      <c r="J96" t="n">
+        <v>36</v>
+      </c>
+      <c r="K96" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>REVO Insurance S.p.A.</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>IT0005513202</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>23.20000076293945</v>
+      </c>
+      <c r="I97" t="n">
+        <v>1.163793065176567</v>
+      </c>
+      <c r="J97" t="n">
+        <v>36</v>
+      </c>
+      <c r="K97" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>VALSOIA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>IT0001018362</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>10.44999980926514</v>
+      </c>
+      <c r="I98" t="n">
+        <v>3.636363702735056</v>
+      </c>
+      <c r="J98" t="n">
+        <v>36</v>
+      </c>
+      <c r="K98" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>WIIT S.p.A.</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>IT0005440893</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="I99" t="n">
+        <v>1.16504854368932</v>
+      </c>
+      <c r="J99" t="n">
+        <v>36</v>
+      </c>
+      <c r="K99" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Banca Profilo S.p.A.</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>IT0001073045</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>0.1490000039339066</v>
+      </c>
+      <c r="I100" t="n">
+        <v>4.6979864531447</v>
+      </c>
+      <c r="J100" t="n">
+        <v>29</v>
+      </c>
+      <c r="K100" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Basic Net S.p.A.</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>IT0001033700</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>6.320000171661377</v>
+      </c>
+      <c r="I101" t="n">
+        <v>2.531645500856685</v>
+      </c>
+      <c r="J101" t="n">
+        <v>29</v>
+      </c>
+      <c r="K101" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>EDISON S.p.A.</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>IT0003372205</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>2.255000114440918</v>
+      </c>
+      <c r="I102" t="n">
+        <v>2.882483224002649</v>
+      </c>
+      <c r="J102" t="n">
+        <v>29</v>
+      </c>
+      <c r="K102" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Fiera Milano S.p.A</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>IT0003365613</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>7.190000057220459</v>
+      </c>
+      <c r="I103" t="n">
+        <v>3.477051432690058</v>
+      </c>
+      <c r="J103" t="n">
+        <v>29</v>
+      </c>
+      <c r="K103" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Ferrari N.V.</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>3.615</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>NL0011585146</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>278.2999877929688</v>
+      </c>
+      <c r="I104" t="n">
+        <v>1.298958016013012</v>
+      </c>
+      <c r="J104" t="n">
+        <v>22</v>
+      </c>
+      <c r="K104" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Generalfinance S.p.A.</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>IT0005144784</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>26.20000076293945</v>
+      </c>
+      <c r="I105" t="n">
+        <v>5.190839543500142</v>
+      </c>
+      <c r="J105" t="n">
+        <v>22</v>
+      </c>
+      <c r="K105" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>MAIRE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>IT0004931058</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>12.97000026702881</v>
+      </c>
+      <c r="I106" t="n">
+        <v>4.510408542451117</v>
+      </c>
+      <c r="J106" t="n">
+        <v>22</v>
+      </c>
+      <c r="K106" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>IT0000062957</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>16.68000030517578</v>
+      </c>
+      <c r="I107" t="n">
+        <v>3.776978348162931</v>
+      </c>
+      <c r="J107" t="n">
+        <v>22</v>
+      </c>
+      <c r="K107" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Prysmian S.p.A.</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>IT0004176001</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>94.05999755859375</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.9568360869235126</v>
+      </c>
+      <c r="J108" t="n">
+        <v>22</v>
+      </c>
+      <c r="K108" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Unicredit S.p.A.</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1.7208</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>IT0005239360</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>60.22000122070312</v>
+      </c>
+      <c r="I109" t="n">
+        <v>2.857522359877342</v>
+      </c>
+      <c r="J109" t="n">
+        <v>22</v>
+      </c>
+      <c r="K109" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -969,7 +5575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C301"/>
+  <dimension ref="A1:C331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1094,7 +5700,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1111,7 +5717,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1128,7 +5734,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1145,7 +5751,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1179,7 +5785,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1196,7 +5802,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1213,7 +5819,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1223,14 +5829,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1240,14 +5846,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1264,7 +5870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1281,7 +5887,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1298,7 +5904,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1308,14 +5914,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1325,14 +5931,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1349,7 +5955,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1383,7 +5989,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1417,7 +6023,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1434,7 +6040,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1451,7 +6057,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1468,7 +6074,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1587,7 +6193,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1604,7 +6210,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1614,14 +6220,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1638,7 +6244,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1648,14 +6254,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1672,7 +6278,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1689,7 +6295,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1706,7 +6312,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1723,7 +6329,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1740,7 +6346,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1757,7 +6363,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1791,7 +6397,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1801,14 +6407,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1825,7 +6431,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1835,14 +6441,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1852,14 +6458,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1869,14 +6475,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1893,7 +6499,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2029,7 +6635,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2046,7 +6652,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2056,14 +6662,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2080,7 +6686,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2090,14 +6696,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2131,7 +6737,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2233,7 +6839,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2301,7 +6907,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2318,7 +6924,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2335,7 +6941,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2352,7 +6958,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2403,7 +7009,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2413,14 +7019,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2437,7 +7043,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2454,7 +7060,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2464,7 +7070,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2505,7 +7111,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2515,14 +7121,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2532,14 +7138,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2549,14 +7155,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2566,7 +7172,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -2583,14 +7189,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2600,14 +7206,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2617,14 +7223,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2634,7 +7240,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2743,7 +7349,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2753,14 +7359,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2770,7 +7376,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -2845,7 +7451,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2855,14 +7461,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2879,7 +7485,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2889,14 +7495,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2906,14 +7512,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2923,14 +7529,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2940,14 +7546,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2957,14 +7563,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2974,14 +7580,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2991,14 +7597,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3008,14 +7614,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3025,14 +7631,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3049,7 +7655,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3059,14 +7665,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3076,14 +7682,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Autostrade Meridionali S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3093,14 +7699,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3110,14 +7716,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3134,7 +7740,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3144,14 +7750,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>Autostrade Meridionali S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3161,14 +7767,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3202,7 +7808,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3219,7 +7825,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3229,14 +7835,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3253,7 +7859,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3270,7 +7876,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3280,14 +7886,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3304,7 +7910,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3321,7 +7927,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3338,7 +7944,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3355,7 +7961,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3365,14 +7971,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3382,14 +7988,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3406,7 +8012,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3416,14 +8022,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3440,7 +8046,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3457,7 +8063,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>TESSELLIS S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3467,14 +8073,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>TESSELLIS S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3484,14 +8090,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3501,14 +8107,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3518,14 +8124,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3542,7 +8148,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3552,14 +8158,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3576,7 +8182,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3593,7 +8199,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3610,7 +8216,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -3620,7 +8226,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -3644,7 +8250,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -3654,14 +8260,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -3671,14 +8277,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -3688,14 +8294,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -3705,7 +8311,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -3729,7 +8335,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -3763,7 +8369,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -3773,14 +8379,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -3790,14 +8396,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -3814,7 +8420,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3824,7 +8430,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -3841,7 +8447,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -3865,7 +8471,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -3875,14 +8481,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -3892,14 +8498,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -3909,14 +8515,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -3926,14 +8532,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -3950,7 +8556,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -3967,7 +8573,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -3984,7 +8590,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4001,7 +8607,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4011,14 +8617,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4028,14 +8634,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4052,7 +8658,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4069,7 +8675,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4086,7 +8692,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4096,14 +8702,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4113,14 +8719,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4130,14 +8736,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4154,7 +8760,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4171,7 +8777,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4181,14 +8787,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4205,7 +8811,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4222,29 +8828,29 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4256,29 +8862,29 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4290,12 +8896,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4324,7 +8930,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4341,7 +8947,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4358,7 +8964,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4375,7 +8981,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4392,7 +8998,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4409,7 +9015,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4419,19 +9025,19 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4443,12 +9049,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4460,12 +9066,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4477,12 +9083,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4494,12 +9100,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4511,80 +9117,80 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4596,12 +9202,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -4613,29 +9219,29 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -4647,29 +9253,29 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -4681,12 +9287,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -4698,29 +9304,29 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -4732,12 +9338,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -4749,12 +9355,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -4766,29 +9372,29 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -4800,29 +9406,29 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -4834,29 +9440,29 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -4868,12 +9474,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -4885,29 +9491,29 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -4919,12 +9525,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -4936,12 +9542,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -4953,46 +9559,46 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5004,12 +9610,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5021,46 +9627,46 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -5072,12 +9678,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -5089,12 +9695,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -5106,7 +9712,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5123,7 +9729,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -5140,7 +9746,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -5157,7 +9763,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -5174,7 +9780,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -5191,7 +9797,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -5208,7 +9814,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -5218,14 +9824,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -5242,7 +9848,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -5259,7 +9865,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5276,7 +9882,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5293,12 +9899,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -5310,12 +9916,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -5327,12 +9933,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -5344,12 +9950,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -5361,12 +9967,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -5378,12 +9984,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -5395,12 +10001,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -5412,12 +10018,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -5429,12 +10035,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -5446,12 +10052,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -5463,12 +10069,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -5480,12 +10086,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -5497,29 +10103,29 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -5531,46 +10137,46 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -5582,12 +10188,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -5599,12 +10205,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -5616,12 +10222,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -5633,7 +10239,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -5650,7 +10256,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -5667,7 +10273,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -5684,7 +10290,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -5701,7 +10307,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -5718,7 +10324,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -5735,7 +10341,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -5745,14 +10351,14 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -5762,14 +10368,14 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -5786,7 +10392,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -5796,14 +10402,14 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -5820,7 +10426,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -5837,7 +10443,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -5854,7 +10460,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -5864,14 +10470,14 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -5888,7 +10494,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -5905,7 +10511,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -5922,7 +10528,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -5932,14 +10538,14 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -5949,14 +10555,14 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -5973,7 +10579,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -5990,7 +10596,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -6000,14 +10606,14 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -6024,7 +10630,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -6041,7 +10647,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -6058,7 +10664,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -6075,17 +10681,527 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
+          <t>Acinque S.p.A.</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>A2A S.p.A.</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>BIESSE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>SIAV S.p.A.</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>SAFILO GROUP S.p.A.</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Renovalo S.p.A.</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>RAI WAY S.p.A.</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Predict S.p.A.</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>CY4Gate S.p.A.</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Porto Aviation Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Orsero S.p.A.</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
           <t>OLIDATA S.p.A.</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr">
+      <c r="B314" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr">
+      <c r="C314" t="inlineStr">
         <is>
           <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>LU-VE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Intred S.p.A.</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>International Care Company S.p.A.</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Avio S.p.A.</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Directa SIM S.P.A.</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>MARR S.p.A.</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>ENA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>FNM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>G.M. Leather S.p.A.</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Gambero Rosso S.p.A.</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Giglio.com S.p.A.</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>HELYX INDUSTRIES S.p.A.</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>ISCC FINTECH S.p.A.</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Enervit S.p.A.</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Cogefeed S.p.A.</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -6113,7 +11229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6136,7 +11252,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6153,12 +11269,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -6170,7 +11286,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6187,12 +11303,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6204,7 +11320,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6221,12 +11337,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6238,7 +11354,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -6248,14 +11364,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6272,7 +11388,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6289,7 +11405,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6298,771 +11414,6 @@
         </is>
       </c>
       <c r="C11" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>BORGOSESIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>BolognaFiere S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CALTAGIRONE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CY4Gate S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Cogefeed S.p.A.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Comer Industries S.p.A.</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Copernico SIM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Directa SIM S.P.A.</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>ENA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Enervit S.p.A.</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>FNM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>G.M. Leather S.p.A.</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Gambero Rosso S.p.A.</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Giglio.com S.p.A.</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>ISCC FINTECH S.p.A.</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>OLIDATA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Orsero S.p.A.</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Porto Aviation Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Predict S.p.A.</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>RAI WAY S.p.A.</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Renovalo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>SAFILO GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>SIAV S.p.A.</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Telmes S.p.A.</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>TradeLab S.p.A.</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>VINEXT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Yakkyo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>ZEST S.p.A.</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>doValue S.p.A.</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
         <is>
           <t>Annual General Meeting</t>
         </is>
